--- a/data/trans_dic/P57_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P57_R2-Edad-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,47; 48,28</t>
+          <t>38,58; 47,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,64; 74,56</t>
+          <t>58,26; 74,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,92; 48,72</t>
+          <t>38,51; 48,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,78; 66,26</t>
+          <t>51,79; 66,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,11; 46,92</t>
+          <t>39,99; 46,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,96; 68,85</t>
+          <t>57,83; 69,06</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,51; 37,69</t>
+          <t>29,57; 37,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47,01; 59,91</t>
+          <t>47,1; 59,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,51; 39,45</t>
+          <t>31,49; 39,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,06; 55,96</t>
+          <t>28,26; 56,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,6; 36,89</t>
+          <t>31,36; 37,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,3; 55,59</t>
+          <t>36,47; 55,44</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,11; 37,13</t>
+          <t>30,03; 37,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48,14; 57,02</t>
+          <t>47,85; 57,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,91; 34,36</t>
+          <t>27,23; 34,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47,45; 54,48</t>
+          <t>47,84; 54,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,61; 34,79</t>
+          <t>29,45; 34,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,21; 54,67</t>
+          <t>49,14; 54,95</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,15; 30,57</t>
+          <t>23,08; 30,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,56; 82,64</t>
+          <t>44,34; 83,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,27; 26,21</t>
+          <t>19,05; 25,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,89; 40,73</t>
+          <t>31,7; 41,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,2; 27,11</t>
+          <t>22,15; 27,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,68; 71,05</t>
+          <t>40,42; 69,77</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,73; 29,89</t>
+          <t>21,91; 30,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,27; 39,21</t>
+          <t>31,43; 39,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,42; 24,11</t>
+          <t>16,12; 24,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,54; 34,3</t>
+          <t>28,58; 34,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,05; 25,83</t>
+          <t>20,16; 26,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,98; 35,91</t>
+          <t>30,95; 35,93</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,14; 29,85</t>
+          <t>20,05; 29,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,64; 43,73</t>
+          <t>35,19; 43,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,65; 21,23</t>
+          <t>13,18; 20,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,46; 34,58</t>
+          <t>8,69; 34,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,42; 23,72</t>
+          <t>17,31; 23,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,43; 37,33</t>
+          <t>14,44; 37,18</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,43; 23,13</t>
+          <t>14,72; 23,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,97; 36,88</t>
+          <t>28,13; 37,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,27; 17,23</t>
+          <t>9,23; 17,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,57; 28,72</t>
+          <t>22,62; 28,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,43; 18,55</t>
+          <t>12,57; 18,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,88; 31,03</t>
+          <t>25,63; 30,99</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,9; 32,18</t>
+          <t>28,92; 32,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>46,31; 62,22</t>
+          <t>46,32; 61,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,88; 27,82</t>
+          <t>24,88; 27,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30,84; 41,11</t>
+          <t>30,17; 40,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,15; 29,37</t>
+          <t>27,22; 29,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,66; 50,15</t>
+          <t>40,55; 50,22</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1425,32 +1425,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>161381; 202514</t>
+          <t>161837; 201264</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>234536; 298238</t>
+          <t>233030; 297304</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>152848; 191357</t>
+          <t>151237; 191124</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>162186; 207538</t>
+          <t>162212; 207422</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>325744; 381072</t>
+          <t>324829; 379707</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>413329; 490997</t>
+          <t>412423; 492551</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1543,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>172934; 220827</t>
+          <t>173253; 217698</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>199092; 253751</t>
+          <t>199506; 250534</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>176171; 220571</t>
+          <t>176075; 221153</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>153471; 285709</t>
+          <t>144280; 286686</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>361884; 422387</t>
+          <t>359080; 424800</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>348449; 519241</t>
+          <t>340649; 517867</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>200634; 247360</t>
+          <t>200080; 250165</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>258196; 305821</t>
+          <t>256654; 306048</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>177735; 226909</t>
+          <t>179871; 225097</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>257069; 295146</t>
+          <t>259205; 295379</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>392787; 461539</t>
+          <t>390688; 457714</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>530494; 589436</t>
+          <t>529826; 592379</t>
         </is>
       </c>
     </row>
@@ -1779,32 +1779,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>148787; 196472</t>
+          <t>148353; 196035</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>395597; 733669</t>
+          <t>393604; 740368</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>124418; 169248</t>
+          <t>123018; 166085</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>225498; 287965</t>
+          <t>224137; 289858</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>286035; 349322</t>
+          <t>285461; 351215</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>648755; 1133095</t>
+          <t>644694; 1112681</t>
         </is>
       </c>
     </row>
@@ -1897,32 +1897,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>103627; 142554</t>
+          <t>104491; 143422</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>174335; 218608</t>
+          <t>175196; 218387</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>81421; 119547</t>
+          <t>79911; 120800</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>155520; 186911</t>
+          <t>155730; 189236</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>194992; 251238</t>
+          <t>196128; 253387</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>341537; 395846</t>
+          <t>341155; 396141</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2015,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66952; 99205</t>
+          <t>66627; 96572</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>130449; 160044</t>
+          <t>128798; 158720</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47785; 80207</t>
+          <t>49795; 79230</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57443; 210013</t>
+          <t>52769; 209073</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>123731; 168433</t>
+          <t>122954; 167166</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>150166; 363310</t>
+          <t>140546; 361879</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>37094; 59453</t>
+          <t>37826; 60435</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>77888; 102705</t>
+          <t>78350; 104661</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36746; 68304</t>
+          <t>36590; 67933</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>93786; 119314</t>
+          <t>93984; 119358</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>81225; 121211</t>
+          <t>82173; 122318</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>179593; 215344</t>
+          <t>177823; 215085</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>977133; 1087918</t>
+          <t>977737; 1087075</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1597551; 2146360</t>
+          <t>1598032; 2134364</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>877663; 981482</t>
+          <t>877838; 976656</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1122807; 1496713</t>
+          <t>1098223; 1489538</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1875864; 2028846</t>
+          <t>1880581; 2033723</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2883072; 3555898</t>
+          <t>2875021; 3560702</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P57_R2-Edad-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>62,15%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,58; 47,98</t>
+          <t>38,12; 48,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,26; 74,33</t>
+          <t>57,86; 72,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,51; 48,66</t>
+          <t>38,61; 48,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,79; 66,23</t>
+          <t>50,86; 65,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,99; 46,75</t>
+          <t>39,6; 46,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,83; 69,06</t>
+          <t>56,7; 66,97</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>53,82%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,57; 37,15</t>
+          <t>29,24; 37,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47,1; 59,15</t>
+          <t>47,34; 59,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,49; 39,56</t>
+          <t>31,16; 39,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,26; 56,15</t>
+          <t>49,78; 59,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,36; 37,1</t>
+          <t>31,8; 37,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,47; 55,44</t>
+          <t>49,98; 57,63</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>50,49%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,03; 37,55</t>
+          <t>30,12; 37,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47,85; 57,06</t>
+          <t>46,47; 55,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,23; 34,08</t>
+          <t>27,23; 34,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47,84; 54,52</t>
+          <t>46,97; 54,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,45; 34,5</t>
+          <t>29,53; 34,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,14; 54,95</t>
+          <t>47,74; 53,19</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>42,05%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,08; 30,5</t>
+          <t>23,2; 30,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,34; 83,39</t>
+          <t>42,01; 49,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,05; 25,72</t>
+          <t>19,25; 25,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,7; 41,0</t>
+          <t>35,65; 41,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,15; 27,26</t>
+          <t>22,2; 27,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,42; 69,77</t>
+          <t>39,53; 44,34</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,91; 30,08</t>
+          <t>22,26; 30,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,43; 39,17</t>
+          <t>32,13; 39,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,12; 24,36</t>
+          <t>16,14; 23,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,58; 34,73</t>
+          <t>28,67; 34,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,16; 26,05</t>
+          <t>19,93; 25,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,95; 35,93</t>
+          <t>30,99; 35,72</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,05; 29,06</t>
+          <t>20,33; 29,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,19; 43,36</t>
+          <t>36,01; 44,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,18; 20,97</t>
+          <t>13,0; 20,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,69; 34,42</t>
+          <t>30,55; 37,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,31; 23,54</t>
+          <t>17,48; 23,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,44; 37,18</t>
+          <t>34,13; 39,64</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,72; 23,52</t>
+          <t>14,37; 23,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,13; 37,58</t>
+          <t>28,26; 37,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,23; 17,13</t>
+          <t>9,35; 17,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,62; 28,73</t>
+          <t>22,51; 28,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,57; 18,72</t>
+          <t>12,48; 18,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,63; 30,99</t>
+          <t>26,04; 31,32</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,92; 32,15</t>
+          <t>28,83; 31,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>46,32; 61,87</t>
+          <t>44,43; 48,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,88; 27,68</t>
+          <t>24,87; 28,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30,17; 40,92</t>
+          <t>39,66; 42,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,22; 29,44</t>
+          <t>27,24; 29,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,55; 50,22</t>
+          <t>42,54; 44,93</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>268252</t>
+          <t>268737</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>185497</t>
+          <t>209999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>453749</t>
+          <t>478735</t>
         </is>
       </c>
     </row>
@@ -1425,32 +1425,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>161837; 201264</t>
+          <t>159910; 202446</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>233030; 297304</t>
+          <t>235949; 297316</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>151237; 191124</t>
+          <t>151630; 189028</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>162212; 207422</t>
+          <t>184363; 236025</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>324829; 379707</t>
+          <t>321636; 380175</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>412423; 492551</t>
+          <t>436798; 515864</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>226278</t>
+          <t>254974</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>240097</t>
+          <t>270847</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>466375</t>
+          <t>525820</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1543,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>173253; 217698</t>
+          <t>171313; 217194</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>199506; 250534</t>
+          <t>225767; 282934</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>176075; 221153</t>
+          <t>174210; 218737</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>144280; 286686</t>
+          <t>248960; 295150</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>359080; 424800</t>
+          <t>364169; 425817</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>340649; 517867</t>
+          <t>488313; 563028</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>281038</t>
+          <t>314114</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278091</t>
+          <t>313014</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>559129</t>
+          <t>627127</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>200080; 250165</t>
+          <t>200702; 248525</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>256654; 306048</t>
+          <t>288526; 342855</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>179871; 225097</t>
+          <t>179826; 224973</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>259205; 295379</t>
+          <t>291811; 336152</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>390688; 457714</t>
+          <t>391720; 460815</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>529826; 592379</t>
+          <t>593017; 660768</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>540461</t>
+          <t>319751</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>264998</t>
+          <t>282414</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>805459</t>
+          <t>602165</t>
         </is>
       </c>
     </row>
@@ -1779,32 +1779,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>148353; 196035</t>
+          <t>149156; 195340</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>393604; 740368</t>
+          <t>294348; 348354</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>123018; 166085</t>
+          <t>124306; 166504</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>224137; 289858</t>
+          <t>260773; 304310</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>285461; 351215</t>
+          <t>286045; 351595</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>644694; 1112681</t>
+          <t>566073; 634969</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>196324</t>
+          <t>214061</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171703</t>
+          <t>191131</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>368027</t>
+          <t>405192</t>
         </is>
       </c>
     </row>
@@ -1897,32 +1897,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>104491; 143422</t>
+          <t>106162; 146089</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>175196; 218387</t>
+          <t>194428; 238661</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79911; 120800</t>
+          <t>80004; 117382</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>155730; 189236</t>
+          <t>173679; 209081</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>196128; 253387</t>
+          <t>193828; 252434</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>341155; 396141</t>
+          <t>375321; 432499</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>144672</t>
+          <t>162847</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135187</t>
+          <t>147740</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>279859</t>
+          <t>310586</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2015,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66627; 96572</t>
+          <t>67573; 98231</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>128798; 158720</t>
+          <t>145803; 179576</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49795; 79230</t>
+          <t>49101; 79165</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52769; 209073</t>
+          <t>133820; 162484</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>122954; 167166</t>
+          <t>124164; 169414</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>140546; 361879</t>
+          <t>287658; 334138</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>90119</t>
+          <t>99902</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>105811</t>
+          <t>115932</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>195930</t>
+          <t>215834</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>37826; 60435</t>
+          <t>36937; 59346</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>78350; 104661</t>
+          <t>86377; 113626</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36590; 67933</t>
+          <t>37057; 71244</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>93984; 119358</t>
+          <t>102096; 131113</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>82173; 122318</t>
+          <t>81579; 121156</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>177823; 215085</t>
+          <t>197703; 237816</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1747144</t>
+          <t>1634384</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1381383</t>
+          <t>1531076</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3128528</t>
+          <t>3165460</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>977737; 1087075</t>
+          <t>974570; 1080195</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1598032; 2134364</t>
+          <t>1564810; 1698228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>877838; 976656</t>
+          <t>877364; 988351</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1098223; 1489538</t>
+          <t>1472474; 1587964</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1880581; 2033723</t>
+          <t>1881644; 2035801</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2875021; 3560702</t>
+          <t>3077618; 3250344</t>
         </is>
       </c>
     </row>
